--- a/gu_in/ItemSetEffect.edf/SetItemEff.xlsx
+++ b/gu_in/ItemSetEffect.edf/SetItemEff.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93DAC08-B534-4E91-8F55-241E79155531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E720EB-F348-4CE3-A1E4-FD8ED41DED2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6534,8 +6534,8 @@
       <c r="N5" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>49</v>
+      <c r="O5" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P5" s="2">
         <v>7</v>
@@ -9384,8 +9384,8 @@
       <c r="N35" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>49</v>
+      <c r="O35" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P35" s="2">
         <v>7</v>
@@ -12234,8 +12234,8 @@
       <c r="N65" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>49</v>
+      <c r="O65" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P65" s="2">
         <v>7</v>
@@ -15084,8 +15084,8 @@
       <c r="N95" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O95" s="2" t="s">
-        <v>49</v>
+      <c r="O95" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P95" s="2">
         <v>7</v>
@@ -17934,8 +17934,8 @@
       <c r="N125" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O125" s="2" t="s">
-        <v>49</v>
+      <c r="O125" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P125" s="2">
         <v>7</v>
@@ -20784,8 +20784,8 @@
       <c r="N155" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O155" s="2" t="s">
-        <v>49</v>
+      <c r="O155" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P155" s="2">
         <v>7</v>
@@ -23634,8 +23634,8 @@
       <c r="N185" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O185" s="2" t="s">
-        <v>49</v>
+      <c r="O185" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P185" s="2">
         <v>7</v>
@@ -26484,8 +26484,8 @@
       <c r="N215" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O215" s="2" t="s">
-        <v>49</v>
+      <c r="O215" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P215" s="2">
         <v>7</v>
@@ -29334,8 +29334,8 @@
       <c r="N245" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="O245" s="2" t="s">
-        <v>49</v>
+      <c r="O245" s="3" t="s">
+        <v>1903</v>
       </c>
       <c r="P245" s="2">
         <v>7</v>
